--- a/template.xlsx
+++ b/template.xlsx
@@ -691,7 +691,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
